--- a/数据库信息/基础信息/教师学历信息.xlsx
+++ b/数据库信息/基础信息/教师学历信息.xlsx
@@ -49490,7 +49490,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
         <v>675</v>
@@ -50167,7 +50167,6 @@
       <c r="C34" t="s">
         <v>29</v>
       </c>
-      <c r="D34"/>
       <c r="E34" t="s">
         <v>53</v>
       </c>
@@ -52042,8 +52041,6 @@
       <c r="A121" s="8" t="s">
         <v>508</v>
       </c>
-      <c r="B121"/>
-      <c r="C121"/>
       <c r="H121">
         <v>146</v>
       </c>
@@ -59369,11 +59366,9 @@
       <c r="C453" t="s">
         <v>56</v>
       </c>
-      <c r="D453"/>
       <c r="E453" t="s">
         <v>57</v>
       </c>
-      <c r="F453"/>
       <c r="G453" t="s">
         <v>58</v>
       </c>
@@ -61500,7 +61495,6 @@
       <c r="C549" t="s">
         <v>25</v>
       </c>
-      <c r="D549"/>
       <c r="E549" t="s">
         <v>47</v>
       </c>
@@ -62250,7 +62244,6 @@
       <c r="C583" t="s">
         <v>29</v>
       </c>
-      <c r="D583"/>
       <c r="E583" t="s">
         <v>41</v>
       </c>
@@ -63614,9 +63607,6 @@
       <c r="C643" t="s">
         <v>14</v>
       </c>
-      <c r="D643"/>
-      <c r="E643"/>
-      <c r="F643"/>
       <c r="H643">
         <v>3</v>
       </c>
@@ -64195,9 +64185,6 @@
       <c r="C671" t="s">
         <v>14</v>
       </c>
-      <c r="D671"/>
-      <c r="E671"/>
-      <c r="F671"/>
       <c r="H671">
         <v>2</v>
       </c>
